--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N102_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N102_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>57.90077719685635</v>
+        <v>9.408876294489156</v>
       </c>
       <c r="D2" t="n">
-        <v>54.67302557632085</v>
+        <v>8.884366656152139</v>
       </c>
       <c r="E2" t="n">
-        <v>21.07630886854477</v>
+        <v>3.424900191138525</v>
       </c>
       <c r="F2" t="n">
-        <v>14.34029266482888</v>
+        <v>2.330297558034693</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.37780600647895</v>
+        <v>4.448893476052829</v>
       </c>
       <c r="D3" t="n">
-        <v>23.83086315881425</v>
+        <v>3.872515263307316</v>
       </c>
       <c r="E3" t="n">
-        <v>21.07630886854477</v>
+        <v>3.424900191138525</v>
       </c>
       <c r="F3" t="n">
-        <v>14.34029266482888</v>
+        <v>2.330297558034693</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3.040009542101258</v>
+        <v>0.4940015505914544</v>
       </c>
       <c r="D4" t="n">
-        <v>4.263843666434242</v>
+        <v>0.6928745957955643</v>
       </c>
       <c r="E4" t="n">
-        <v>21.07630886854477</v>
+        <v>3.424900191138525</v>
       </c>
       <c r="F4" t="n">
-        <v>14.34029266482888</v>
+        <v>2.330297558034693</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8.162411061867882</v>
+        <v>1.326391797553531</v>
       </c>
       <c r="D5" t="n">
-        <v>16.09976986389988</v>
+        <v>2.61621260288373</v>
       </c>
       <c r="E5" t="n">
-        <v>21.07630886854477</v>
+        <v>3.424900191138525</v>
       </c>
       <c r="F5" t="n">
-        <v>14.34029266482888</v>
+        <v>2.330297558034693</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.98714898445991</v>
+        <v>5.685411709974736</v>
       </c>
       <c r="D6" t="n">
-        <v>24.67005640842769</v>
+        <v>4.0088841663695</v>
       </c>
       <c r="E6" t="n">
-        <v>21.07630886854477</v>
+        <v>3.424900191138525</v>
       </c>
       <c r="F6" t="n">
-        <v>14.34029266482888</v>
+        <v>2.330297558034693</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>53.43578767350286</v>
+        <v>8.683315496944214</v>
       </c>
       <c r="D7" t="n">
-        <v>9.900712497534945</v>
+        <v>1.608865780849429</v>
       </c>
       <c r="E7" t="n">
-        <v>21.07630886854477</v>
+        <v>3.424900191138525</v>
       </c>
       <c r="F7" t="n">
-        <v>14.34029266482888</v>
+        <v>2.330297558034693</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>47.71738031706023</v>
+        <v>7.754074301522288</v>
       </c>
       <c r="D8" t="n">
-        <v>19.98853126051791</v>
+        <v>3.24813632983416</v>
       </c>
       <c r="E8" t="n">
-        <v>21.07630886854477</v>
+        <v>3.424900191138525</v>
       </c>
       <c r="F8" t="n">
-        <v>14.34029266482888</v>
+        <v>2.330297558034693</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>62.50326721390534</v>
+        <v>10.15678092225962</v>
       </c>
       <c r="D9" t="n">
-        <v>30.69264290212948</v>
+        <v>4.987554471596041</v>
       </c>
       <c r="E9" t="n">
-        <v>21.07630886854477</v>
+        <v>3.424900191138525</v>
       </c>
       <c r="F9" t="n">
-        <v>14.34029266482888</v>
+        <v>2.330297558034693</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
